--- a/KiCad_files/MusselGapeTracker_RevI/MusselGapeTracker_RevI_PurchaseList.xlsx
+++ b/KiCad_files/MusselGapeTracker_RevI/MusselGapeTracker_RevI_PurchaseList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Documents/GitHub/MusselGapeTracker_hardware/KiCad_files/MusselGapeTracker_RevI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474AA497-80AC-A044-BDC9-BFE30F811261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B308918-D192-9C4E-A4D8-B30E4510915C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="1020" windowWidth="27640" windowHeight="16680" xr2:uid="{E7DEF6FF-2B66-CB45-A28F-80AEC1E72622}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
   <si>
     <t xml:space="preserve">MusselGapeTracker RevI Purchase List </t>
   </si>
@@ -327,13 +327,26 @@
   </si>
   <si>
     <t>CN306-100-ND</t>
+  </si>
+  <si>
+    <t>MusselGapeTracker_RevI circuit board (order of 3)</t>
+  </si>
+  <si>
+    <t>Hall effect sensor board (order in multiples of 3, up to 16 per datalogger)</t>
+  </si>
+  <si>
+    <t>https://oshpark.com/shared_projects/lujm2dur</t>
+  </si>
+  <si>
+    <t>https://oshpark.com/shared_projects/L2bLLtKh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
@@ -433,7 +446,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -480,6 +493,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1630,21 +1644,41 @@
       <c r="E52" s="6"/>
       <c r="F52" s="15"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" s="2"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="15"/>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" s="19"/>
-      <c r="B54" s="7"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="15"/>
+    <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="7">
+        <v>1</v>
+      </c>
+      <c r="D53" s="22">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="E53" s="22">
+        <f>D53/3</f>
+        <v>10.816666666666668</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="7">
+        <v>16</v>
+      </c>
+      <c r="D54" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="E54" s="22">
+        <f>D54*B54</f>
+        <v>8</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B56" s="7"/>

--- a/KiCad_files/MusselGapeTracker_RevI/MusselGapeTracker_RevI_PurchaseList.xlsx
+++ b/KiCad_files/MusselGapeTracker_RevI/MusselGapeTracker_RevI_PurchaseList.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Documents/GitHub/MusselGapeTracker_hardware/KiCad_files/MusselGapeTracker_RevI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B308918-D192-9C4E-A4D8-B30E4510915C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837CC0D3-9025-F64E-A65B-8629E3A028DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="1020" windowWidth="27640" windowHeight="16680" xr2:uid="{E7DEF6FF-2B66-CB45-A28F-80AEC1E72622}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="143">
   <si>
     <t xml:space="preserve">MusselGapeTracker RevI Purchase List </t>
   </si>
@@ -83,9 +83,6 @@
     <t>LED, Green 0805</t>
   </si>
   <si>
-    <t>BJT NPN Transistor 50V 2A SOT23-3 package</t>
-  </si>
-  <si>
     <t>Pushbutton switch SPST tactile, SMD</t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>160-1423-1-ND</t>
   </si>
   <si>
-    <t>FMMT619CT-ND</t>
-  </si>
-  <si>
     <t>SW836CT-ND</t>
   </si>
   <si>
@@ -284,9 +278,6 @@
     <t>Digikey PN</t>
   </si>
   <si>
-    <t>Digikey $</t>
-  </si>
-  <si>
     <t>Extended $</t>
   </si>
   <si>
@@ -339,6 +330,144 @@
   </si>
   <si>
     <t>https://oshpark.com/shared_projects/L2bLLtKh</t>
+  </si>
+  <si>
+    <t>OSH Stencils</t>
+  </si>
+  <si>
+    <t>MusselGapeTracker RevI stencil</t>
+  </si>
+  <si>
+    <t>Hall effect sensor board stencil</t>
+  </si>
+  <si>
+    <t>https://www.oshstencils.com/#</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/panasonic-industry/EEE-FC1V1R0R/817433?s=N4IgTCBcDaIAoGECiAWADGFCAqBaAcgCIgC6AvkA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/kemet/C0603C104K4RACTU/411095?s=N4IgTCBcDaIMwE4EFoCMAGBA2NyByAIiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/kemet/C0603C475M8PACTU/2200892?s=N4IgTCBcDaIMwE4EFoEEYAMHluQOQBEQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/CC0603KRX5R7BB106/7164370?s=N4IgTCBcDaIMwEYEFo4BYAcA2ZZkDkAREAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0603JR-07100RL/726697?s=N4IgTCBcDaIMwEYEFoEAY0HEBKBhAKsgHIAiIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0603JR-074K7L/726785?s=N4IgTCBcDaIMwEYEFoAsA6A7AaQOICUBhAFWQDkAREAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0603JR-0710KL/726700?s=N4IgTCBcDaIMwEYEFoEAYDSBxASgYQBVkA5AERAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0603JR-0715KL/726717?s=N4IgTCBcDaIMwEYEFoEFYDSBxASgYQBVkA5AERAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/yageo/RC0603JR-07100KL/726698?s=N4IgTCBcDaIMwEYEFoEAY0GkDiAlAwgCrIByAIiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/liteon/LTST-C171KRKT/386801?s=N4IgTCBcDaIIwDYAMBaOAWMB2NKByAIiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/liteon/LTST-C171GKT/386793?s=N4IgTCBcDaIIwDYAMBaOAWMBmNKByAIiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/omron-electronics-inc-emc-div/B3S-1000P/368390?s=N4IgTCBcDaIMoHUAcBmAbAYQCoFoByAIiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/allegro-microsystems/A1395SEHLT-T/1190025?s=N4IgTCBcDaIGxgAwFoCMqDsBmZdkDkAREAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/analog-devices-inc-maxim-integrated/DS3231SN/1197576?s=N4IgTCBcDaICIGUDMYkEYEDkDEBaTcIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/keystone-electronics/3000/227440</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/panasonic-energy/CR1220/269740</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/B4B-PH-K-S/926613</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/PHR-4/608606?s=N4IgTCBcDaICwFYEFoCMqBsdkDkAiIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jst-sales-america-inc/SPH-002T-P0-5S/527359?s=N4IgTCBcDaICwFYEFoCMqwHY3IHIBEQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/PPTC041LFBN-RC/810144</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/PRPC040SAAN-RC/2775214?s=N4IgTCBcDaIMoEYAMCEFEDCBaALErAcgCIgC6AvkA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/taiyo-yuden/LBR2012T100K/1788937?s=N4IgTCBcDaIKwA4DsBaMAGALHFBGFAcgCIgC6AvkA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0901310763/760853?s=N4IgTCBcDaIOoFkAcBGAzATgLQDkAiIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/microchip-technology/MCP1700T-3002E-TT/651114?s=N4IgTCBcDaILIGEAKBGA7ABgwFQLQGYswBRAem2wTwDkAREAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/toshiba-semiconductor-and-storage/SSM3J328R-LF/2753199?s=N4IgTCBcDaIMpwLIGYBSywA4BKAZAYgMIAqAtAHIAiIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/texas-instruments/SN74HC595DRG3/2600341?s=N4IgTCBcDa4JwDYC0BmAjADjGJakDkAREAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/5033981892/4555393?s=N4IgTCBcDaIOoFkCMKCcAGAwgFQLQDkAREAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/texas-instruments/CD74HC4067PWR/26639687?s=N4IgTCBcDa4JwDYC0BhAIgdgCwAkVYAYEMAFAdQCUUAVJAOTRAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/microchip-technology/ATMEGA328P-AUR/2357086?s=N4IgTCBcDaIIIBUCyBRA4nAzGAHABQFo4BVAJQGEECA5AERAF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/radial-magnets-inc/8195/555329?s=N4IgTCBcDaICwDYCcBaAjABgwVhQOQBEQBdAXyA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/same-sky-formerly-cui-devices/PJ-202AH/408450?s=N4IgTCBcDaIMIAUC0YAMYCCAJJA5AIiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/mpd-memory-protection-devices/EP501A/2439550?s=N4IgTCBcDaIKIAUCsAGAjAQQLQDkAiIAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sullins-connector-solutions/PPPC061LGBN-RC/775939</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/c-k/PTS525SM15SMTR2-LFS/1146855?s=N4IgTCBcDaIMIGkByBOAjABgCxwCoFokAREAXQF8g</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0022232021/26667?s=N4IgTCBcDaIOoFkAsYAMqC0A5AIiAugL5A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0010112023/171978?s=N4IgTCBcDaIOoFkwDYAMBGAtAOQCIgF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/molex/0469990101/2713548?s=N4IgTCBcDaIOoFkCsYBsAOAtAOQCIgF0BfIA</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/cnc-tech/2725-2828-BE-01000-A/6830180?s=N4IgTCBcDaIMIDkDMAGAbAWgIwpRhAIiALoC%2BQA</t>
+  </si>
+  <si>
+    <t>BJT NPN Transistor 45V 0.2A SOT23-3 package</t>
+  </si>
+  <si>
+    <t>MMBT6429LT1GOSCT-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/onsemi/MMBT6429LT1G/919618</t>
+  </si>
+  <si>
+    <t>Price $</t>
   </si>
 </sst>
 </file>
@@ -446,7 +575,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -465,9 +594,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,6 +620,11 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -830,7 +961,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED75037-60C9-0D48-8DC3-89718E754A3B}">
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="64" bestFit="1" customWidth="1"/>
@@ -850,20 +981,20 @@
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="F2" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -871,12 +1002,12 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="13"/>
+        <v>81</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B5" s="4"/>
@@ -892,887 +1023,1118 @@
       <c r="E6" s="6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="1"/>
+      <c r="B7" s="7"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B8" s="4">
         <v>4</v>
       </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="5">
         <v>0.38</v>
-      </c>
-      <c r="E7" s="6">
-        <f>D7*B7</f>
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="7">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0.08</v>
       </c>
       <c r="E8" s="6">
         <f>D8*B8</f>
-        <v>2.4</v>
+        <v>1.52</v>
+      </c>
+      <c r="F8" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="17" t="s">
-        <v>5</v>
+      <c r="A9" s="16" t="s">
+        <v>4</v>
       </c>
       <c r="B9" s="7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D9" s="6">
-        <v>0.73</v>
+        <v>0.08</v>
       </c>
       <c r="E9" s="6">
         <f>D9*B9</f>
-        <v>2.19</v>
+        <v>2.4</v>
+      </c>
+      <c r="F9" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
-        <v>6</v>
+      <c r="A10" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="B10" s="7">
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" s="6">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="E10" s="6">
         <f>D10*B10</f>
+        <v>2.19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="7">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="6">
+        <v>0.65</v>
+      </c>
+      <c r="E11" s="6">
+        <f>D11*B11</f>
         <v>1.9500000000000002</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="17" t="s">
+      <c r="F11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
         <v>7</v>
-      </c>
-      <c r="B11" s="7">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E11" s="6">
-        <f t="shared" ref="E11:E41" si="0">D11*B11</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="17" t="s">
-        <v>8</v>
       </c>
       <c r="B12" s="7">
         <v>4</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D12" s="6">
         <v>0.1</v>
       </c>
       <c r="E12" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E12:E42" si="0">D12*B12</f>
         <v>0.4</v>
       </c>
+      <c r="F12" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="17" t="s">
-        <v>9</v>
+      <c r="A13" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="B13" s="7">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D13" s="6">
         <v>0.1</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0.4</v>
+      </c>
+      <c r="F13" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="17" t="s">
-        <v>10</v>
+      <c r="A14" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="B14" s="7">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D14" s="6">
         <v>0.1</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
+        <v>3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="17" t="s">
-        <v>11</v>
+      <c r="A15" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="B15" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D15" s="6">
         <v>0.1</v>
       </c>
       <c r="E15" s="6">
         <f t="shared" si="0"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="F15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="7">
+        <v>6</v>
+      </c>
+      <c r="C16" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" si="0"/>
         <v>0.60000000000000009</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="17" t="s">
+      <c r="F16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
         <v>12</v>
-      </c>
-      <c r="B16" s="7">
-        <v>2</v>
-      </c>
-      <c r="C16" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="6">
-        <v>0.13</v>
-      </c>
-      <c r="E16" s="6">
-        <f t="shared" si="0"/>
-        <v>0.26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="17" t="s">
-        <v>13</v>
       </c>
       <c r="B17" s="7">
         <v>2</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D17" s="6">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="E17" s="6">
         <f t="shared" si="0"/>
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="17" t="s">
-        <v>14</v>
+        <v>0.26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>13</v>
       </c>
       <c r="B18" s="7">
         <v>2</v>
       </c>
       <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="6">
+        <v>0.12</v>
+      </c>
+      <c r="E18" s="6">
+        <f t="shared" si="0"/>
+        <v>0.24</v>
+      </c>
+      <c r="F18" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="7">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D19" s="6">
+        <v>0.17</v>
+      </c>
+      <c r="E19" s="6">
+        <f t="shared" si="0"/>
+        <v>0.34</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="7">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.59</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" si="0"/>
+        <v>1.77</v>
+      </c>
+      <c r="F20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" s="7">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
         <v>52</v>
       </c>
-      <c r="D18" s="6">
-        <v>0.62</v>
-      </c>
-      <c r="E18" s="6">
-        <f t="shared" si="0"/>
-        <v>1.24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" s="7">
-        <v>3</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D21" s="6">
+        <v>1.22</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>19.52</v>
+      </c>
+      <c r="F21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="6">
-        <v>0.59</v>
-      </c>
-      <c r="E19" s="6">
-        <f t="shared" si="0"/>
-        <v>1.77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" s="7">
-        <v>16</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D22" s="6">
+        <v>17.21</v>
+      </c>
+      <c r="E22" s="6">
+        <f t="shared" si="0"/>
+        <v>17.21</v>
+      </c>
+      <c r="F22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="7">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="E20" s="6">
-        <f t="shared" si="0"/>
-        <v>19.52</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="B21" s="7">
-        <v>1</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D23" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="0"/>
+        <v>0.4</v>
+      </c>
+      <c r="F23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B24" s="7">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="6">
-        <v>17.21</v>
-      </c>
-      <c r="E21" s="6">
-        <f t="shared" si="0"/>
-        <v>17.21</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="7">
-        <v>1</v>
-      </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="6">
-        <v>0.4</v>
-      </c>
-      <c r="E22" s="6">
-        <f t="shared" si="0"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="17" t="s">
+      <c r="D24" s="6">
+        <v>1.03</v>
+      </c>
+      <c r="E24" s="6">
+        <f t="shared" si="0"/>
+        <v>1.03</v>
+      </c>
+      <c r="F24" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="16" t="s">
         <v>19</v>
-      </c>
-      <c r="B23" s="7">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="6">
-        <v>1.03</v>
-      </c>
-      <c r="E23" s="6">
-        <f t="shared" si="0"/>
-        <v>1.03</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="7">
-        <v>16</v>
-      </c>
-      <c r="C24" t="s">
-        <v>58</v>
-      </c>
-      <c r="D24" s="6">
-        <v>0.2</v>
-      </c>
-      <c r="E24" s="6">
-        <f t="shared" si="0"/>
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="17" t="s">
-        <v>21</v>
       </c>
       <c r="B25" s="7">
         <v>16</v>
       </c>
       <c r="C25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="E25" s="6">
+        <f t="shared" si="0"/>
+        <v>3.2</v>
+      </c>
+      <c r="F25" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" s="7">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="E26" s="6">
+        <f t="shared" si="0"/>
+        <v>1.6</v>
+      </c>
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" s="7">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="6">
+        <v>4.0899999999999999E-2</v>
+      </c>
+      <c r="E27" s="6">
+        <f t="shared" si="0"/>
+        <v>4.09</v>
+      </c>
+      <c r="F27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="7">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D28" s="6">
+        <v>0.37</v>
+      </c>
+      <c r="E28" s="6">
+        <f t="shared" si="0"/>
+        <v>0.37</v>
+      </c>
+      <c r="F28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="7">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="6">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E29" s="6">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="F29" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="7">
+        <v>3</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="6">
         <v>0.1</v>
       </c>
-      <c r="E25" s="6">
-        <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="7">
-        <v>100</v>
-      </c>
-      <c r="C26" t="s">
-        <v>60</v>
-      </c>
-      <c r="D26" s="6">
-        <v>4.0899999999999999E-2</v>
-      </c>
-      <c r="E26" s="6">
-        <f t="shared" si="0"/>
-        <v>4.09</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="7">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>61</v>
-      </c>
-      <c r="D27" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="E27" s="6">
-        <f t="shared" si="0"/>
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="7">
-        <v>1</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="E30" s="6">
+        <f t="shared" si="0"/>
+        <v>0.30000000000000004</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" s="7">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="6">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E28" s="6">
-        <f t="shared" si="0"/>
-        <v>0.55000000000000004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="B29" s="7">
-        <v>1</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D31" s="6">
+        <v>1.8</v>
+      </c>
+      <c r="E31" s="6">
+        <f t="shared" si="0"/>
+        <v>1.8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B32" s="7">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
         <v>63</v>
       </c>
-      <c r="D29" s="6">
-        <v>0.1</v>
-      </c>
-      <c r="E29" s="6">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="B30" s="7">
-        <v>1</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D32" s="6">
+        <v>0.51</v>
+      </c>
+      <c r="E32" s="6">
+        <f t="shared" si="0"/>
+        <v>0.51</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B33" s="7">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="6">
-        <v>1.8</v>
-      </c>
-      <c r="E30" s="6">
-        <f t="shared" si="0"/>
-        <v>1.8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B31" s="7">
-        <v>1</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D33" s="6">
+        <v>0.42</v>
+      </c>
+      <c r="E33" s="6">
+        <f t="shared" si="0"/>
+        <v>0.42</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" s="7">
+        <v>2</v>
+      </c>
+      <c r="C34" t="s">
         <v>65</v>
       </c>
-      <c r="D31" s="6">
-        <v>0.51</v>
-      </c>
-      <c r="E31" s="6">
-        <f t="shared" si="0"/>
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B32" s="7">
-        <v>1</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D34" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="E34" s="6">
+        <f t="shared" si="0"/>
+        <v>1.44</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="7">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
         <v>66</v>
       </c>
-      <c r="D32" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="E32" s="6">
-        <f t="shared" si="0"/>
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="7">
-        <v>2</v>
-      </c>
-      <c r="C33" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="E33" s="6">
-        <f t="shared" si="0"/>
-        <v>1.44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" s="7">
-        <v>1</v>
-      </c>
-      <c r="C34" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="6">
+      <c r="D35" s="6">
         <v>2.62</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E35" s="6">
         <f t="shared" si="0"/>
         <v>2.62</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B35" s="7">
-        <v>1</v>
-      </c>
-      <c r="C35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="E35" s="6">
-        <f t="shared" si="0"/>
-        <v>1.25</v>
+      <c r="F35" s="14" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B36" s="7">
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D36" s="6">
+        <v>1.25</v>
+      </c>
+      <c r="E36" s="6">
+        <f t="shared" si="0"/>
+        <v>1.25</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="7">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>68</v>
+      </c>
+      <c r="D37" s="6">
         <v>2.74</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E37" s="6">
         <f t="shared" si="0"/>
         <v>2.74</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B37" s="7">
-        <v>16</v>
-      </c>
-      <c r="C37" t="s">
-        <v>71</v>
-      </c>
-      <c r="D37" s="6">
-        <v>0.18</v>
-      </c>
-      <c r="E37" s="6">
-        <f t="shared" si="0"/>
-        <v>2.88</v>
+      <c r="F37" s="14" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B38" s="7">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D38" s="6">
-        <v>0.75</v>
+        <v>0.18</v>
       </c>
       <c r="E38" s="6">
         <f t="shared" si="0"/>
-        <v>0.75</v>
+        <v>2.88</v>
+      </c>
+      <c r="F38" s="14" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B39" s="7">
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D39" s="6">
-        <v>1.71</v>
+        <v>0.75</v>
       </c>
       <c r="E39" s="6">
         <f t="shared" si="0"/>
-        <v>1.71</v>
+        <v>0.75</v>
+      </c>
+      <c r="F39" s="14" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B40" s="7">
         <v>1</v>
       </c>
-      <c r="C40" s="8" t="s">
-        <v>74</v>
+      <c r="C40" t="s">
+        <v>71</v>
       </c>
       <c r="D40" s="6">
-        <v>0.64</v>
+        <v>1.71</v>
       </c>
       <c r="E40" s="6">
         <f t="shared" si="0"/>
-        <v>0.64</v>
+        <v>1.71</v>
+      </c>
+      <c r="F40" s="14" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B41" s="7">
         <v>1</v>
       </c>
-      <c r="C41" s="9" t="s">
-        <v>75</v>
+      <c r="C41" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="D41" s="6">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="E41" s="6">
         <f t="shared" si="0"/>
-        <v>0.67</v>
+        <v>0.64</v>
+      </c>
+      <c r="F41" s="14" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B42" s="7">
         <v>1</v>
       </c>
-      <c r="C42" t="s">
-        <v>76</v>
+      <c r="C42" s="24" t="s">
+        <v>73</v>
       </c>
       <c r="D42" s="6">
-        <v>0.16</v>
+        <v>0.67</v>
       </c>
       <c r="E42" s="6">
-        <f>D42*B42</f>
-        <v>0.16</v>
+        <f t="shared" si="0"/>
+        <v>0.67</v>
+      </c>
+      <c r="F42" s="14" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B43" s="7">
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D43" s="6">
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E43" s="6">
         <f>D43*B43</f>
-        <v>0.14000000000000001</v>
+        <v>0.16</v>
+      </c>
+      <c r="F43" s="14" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B44" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D44" s="6">
-        <v>0.15</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E44" s="6">
         <f>D44*B44</f>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="F44" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="7">
+        <v>10</v>
+      </c>
+      <c r="C45" t="s">
+        <v>76</v>
+      </c>
+      <c r="D45" s="6">
+        <v>0.15</v>
+      </c>
+      <c r="E45" s="6">
+        <f>D45*B45</f>
         <v>1.5</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="7"/>
-      <c r="D45" s="6"/>
-      <c r="E45" s="6"/>
+      <c r="F45" s="14" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="3"/>
+      <c r="B46" s="7"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" s="7"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="14"/>
+    </row>
+    <row r="49" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B49" s="7">
+        <v>1</v>
+      </c>
+      <c r="C49" s="13"/>
+      <c r="D49" s="6">
+        <v>9.99</v>
+      </c>
+      <c r="E49" s="6">
+        <f>D49*B49</f>
+        <v>9.99</v>
+      </c>
+      <c r="F49" s="14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" s="7">
+        <v>1</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" s="6">
+        <v>15.9</v>
+      </c>
+      <c r="E50" s="6">
+        <f t="shared" ref="E50" si="1">D50*B50</f>
+        <v>15.9</v>
+      </c>
+      <c r="F50" s="14" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B47" s="7"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="15"/>
-    </row>
-    <row r="48" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A48" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B48" s="7">
-        <v>1</v>
-      </c>
-      <c r="C48" s="14"/>
-      <c r="D48" s="6">
-        <v>9.99</v>
-      </c>
-      <c r="E48" s="6">
-        <f>D48*B48</f>
-        <v>9.99</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A49" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B49" s="7">
-        <v>1</v>
-      </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="6">
-        <v>15.9</v>
-      </c>
-      <c r="E49" s="6">
-        <f t="shared" ref="E49" si="1">D49*B49</f>
-        <v>15.9</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" s="1"/>
-      <c r="B52" s="7"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="6"/>
-      <c r="E52" s="6"/>
-      <c r="F52" s="15"/>
-    </row>
-    <row r="53" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A53" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B53" s="7">
-        <v>1</v>
-      </c>
-      <c r="D53" s="22">
-        <v>32.450000000000003</v>
-      </c>
-      <c r="E53" s="22">
-        <f>D53/3</f>
-        <v>10.816666666666668</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>98</v>
-      </c>
+      <c r="A52" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" s="1"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="14"/>
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B54" s="7">
+        <v>1</v>
+      </c>
+      <c r="D54" s="21">
+        <v>32.450000000000003</v>
+      </c>
+      <c r="E54" s="21">
+        <f>D54/3</f>
+        <v>10.816666666666668</v>
+      </c>
+      <c r="F54" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B55" s="7">
         <v>16</v>
       </c>
-      <c r="D54" s="20">
+      <c r="D55" s="19">
         <v>0.5</v>
       </c>
-      <c r="E54" s="22">
-        <f>D54*B54</f>
+      <c r="E55" s="21">
+        <f>D55*B55</f>
         <v>8</v>
       </c>
-      <c r="F54" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B56" s="7"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="15"/>
+      <c r="F55" s="14" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" s="2"/>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="14"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="15"/>
+      <c r="A57" s="1"/>
+      <c r="B57" s="7"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="14"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B58" s="7"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="6"/>
+      <c r="E58" s="6"/>
+      <c r="F58" s="14"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="2"/>
+      <c r="B59" s="7"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="14"/>
+    </row>
+    <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A60" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="B60" s="7"/>
+      <c r="C60" s="2"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="14"/>
+    </row>
+    <row r="62" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>91</v>
+      </c>
+      <c r="B62" s="7">
+        <v>3</v>
+      </c>
+      <c r="C62" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="D62" s="6">
+        <v>25.89</v>
+      </c>
+      <c r="E62" s="19">
+        <f>D62*B62</f>
+        <v>77.67</v>
+      </c>
+      <c r="F62" s="14" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A64" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B64" s="7"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="6"/>
+      <c r="E64" s="6"/>
+      <c r="F64" s="14"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A66" s="2"/>
-      <c r="B66" s="7"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="15"/>
-    </row>
-    <row r="67" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A67" s="19" t="s">
-        <v>2</v>
-      </c>
+      <c r="A66" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="7">
+        <v>1</v>
+      </c>
+      <c r="C66" s="13"/>
+      <c r="D66" s="6">
+        <v>38.950000000000003</v>
+      </c>
+      <c r="E66" s="19">
+        <f>D66*0</f>
+        <v>0</v>
+      </c>
+      <c r="F66" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="2"/>
       <c r="B67" s="7"/>
-      <c r="C67" s="2"/>
+      <c r="C67" s="13"/>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
-      <c r="F67" s="15"/>
-    </row>
-    <row r="69" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>94</v>
-      </c>
-      <c r="B69" s="7">
-        <v>3</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="D69" s="6">
-        <v>25.89</v>
-      </c>
-      <c r="E69" s="20">
-        <f>D69*B69</f>
-        <v>77.67</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>92</v>
+      <c r="F67" s="14"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B68" s="7"/>
+      <c r="C68" s="13"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="14"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="2"/>
+      <c r="D69" s="22"/>
+    </row>
+    <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
+      <c r="A70" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B70" s="7">
+        <v>1</v>
+      </c>
+      <c r="D70" s="22">
+        <v>12.4</v>
+      </c>
+      <c r="E70" s="23">
+        <f>D70*B70</f>
+        <v>12.4</v>
+      </c>
+      <c r="F70" s="14" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A71" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="B71" s="7"/>
-      <c r="C71" s="2"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="15"/>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>91</v>
-      </c>
-      <c r="B73" s="7">
-        <v>1</v>
-      </c>
-      <c r="C73" s="14"/>
-      <c r="D73" s="6">
-        <v>38.950000000000003</v>
-      </c>
-      <c r="E73" s="20">
-        <f>D73*0</f>
-        <v>0</v>
-      </c>
-      <c r="F73" s="15" t="s">
-        <v>92</v>
-      </c>
+      <c r="A71" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B71" s="7">
+        <v>1</v>
+      </c>
+      <c r="D71" s="22">
+        <v>5</v>
+      </c>
+      <c r="E71" s="23">
+        <f>D71*B71</f>
+        <v>5</v>
+      </c>
+      <c r="F71" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A72" s="18"/>
+      <c r="B72" s="7"/>
+      <c r="C72" s="2"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="6"/>
+      <c r="F72" s="14"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B74" s="7"/>
+      <c r="C74" s="13"/>
+      <c r="D74" s="6"/>
+      <c r="E74" s="19"/>
+      <c r="F74" s="14"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A79" s="1"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="13"/>
+      <c r="D79" s="6"/>
+      <c r="E79" s="19"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A80" s="2"/>
+      <c r="D80" s="22"/>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A81" s="2"/>
+      <c r="B81" s="7"/>
+      <c r="D81" s="22"/>
+      <c r="E81" s="23"/>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A82" s="2"/>
+      <c r="B82" s="7"/>
+      <c r="D82" s="22"/>
+      <c r="E82" s="23"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F48" r:id="rId1" xr:uid="{CE098682-63F2-0540-816D-9DB4E2056C6A}"/>
-    <hyperlink ref="F69" r:id="rId2" xr:uid="{E2F30FA9-C62F-DA44-9F5A-4734E843ADFE}"/>
-    <hyperlink ref="F73" r:id="rId3" xr:uid="{49ECEDB9-2549-2442-BAAE-D7288653DE13}"/>
+    <hyperlink ref="F49" r:id="rId1" xr:uid="{CE098682-63F2-0540-816D-9DB4E2056C6A}"/>
+    <hyperlink ref="F66" r:id="rId2" xr:uid="{66C62E6A-5AA2-D644-B34E-A48C72358DE6}"/>
+    <hyperlink ref="F70" r:id="rId3" xr:uid="{12ACA6E6-5506-E742-AC04-27528FBF953E}"/>
+    <hyperlink ref="F30" r:id="rId4" xr:uid="{AA12B244-D153-094D-83A7-FBA539AD5750}"/>
+    <hyperlink ref="F32" r:id="rId5" xr:uid="{C3E9F65A-EB3D-214D-B488-DDB6862B91C0}"/>
+    <hyperlink ref="F33" r:id="rId6" xr:uid="{9E39EBCE-6E3D-2942-8368-3E163529D205}"/>
+    <hyperlink ref="F34" r:id="rId7" xr:uid="{F126676B-6637-9E45-A4B4-5DF8DB517FD7}"/>
+    <hyperlink ref="F35" r:id="rId8" xr:uid="{98DF1076-0B7F-EE47-842E-EB404B8033ED}"/>
+    <hyperlink ref="F36" r:id="rId9" xr:uid="{956EED86-64A6-B44E-98F2-687B74D9D5F4}"/>
+    <hyperlink ref="F37" r:id="rId10" xr:uid="{560DCB09-EB3B-AC40-9B38-E4B6325C09DF}"/>
+    <hyperlink ref="F38" r:id="rId11" xr:uid="{91C238BE-FB4A-AB46-AAB6-EC4D8C3A4EED}"/>
+    <hyperlink ref="F39" r:id="rId12" xr:uid="{734B7B79-2D6B-394C-BF48-D6BADC55C3A5}"/>
+    <hyperlink ref="F40" r:id="rId13" xr:uid="{C25EC643-8268-4545-939A-B02E47D53C06}"/>
+    <hyperlink ref="F41" r:id="rId14" xr:uid="{8C3D3D1C-D2CA-344B-AF42-73002333ADFB}"/>
+    <hyperlink ref="F42" r:id="rId15" xr:uid="{CA78070B-7B0B-EC40-A9ED-015F2E7BD4A2}"/>
+    <hyperlink ref="F43" r:id="rId16" xr:uid="{16DCD6FD-C866-C94D-9905-D33D250E3D3C}"/>
+    <hyperlink ref="F44" r:id="rId17" xr:uid="{20744DBB-E30C-DB42-8203-F2DDB1766806}"/>
+    <hyperlink ref="F45" r:id="rId18" xr:uid="{33FE962D-90BF-364A-847F-1311083DD8EE}"/>
+    <hyperlink ref="F62" r:id="rId19" xr:uid="{5598F3F1-72B7-DB44-B23B-CE074D88B548}"/>
+    <hyperlink ref="F19" r:id="rId20" xr:uid="{AB860A04-6C4B-D441-8D41-1DB66038BD89}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/KiCad_files/MusselGapeTracker_RevI/MusselGapeTracker_RevI_PurchaseList.xlsx
+++ b/KiCad_files/MusselGapeTracker_RevI/MusselGapeTracker_RevI_PurchaseList.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jack/Documents/GitHub/MusselGapeTracker_hardware/KiCad_files/MusselGapeTracker_RevI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{837CC0D3-9025-F64E-A65B-8629E3A028DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{781FA6FF-897B-9B4A-A077-27D12518E3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1680" yWindow="1020" windowWidth="27640" windowHeight="16680" xr2:uid="{E7DEF6FF-2B66-CB45-A28F-80AEC1E72622}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -575,7 +575,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -605,13 +605,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1050,7 +1047,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B9" s="7">
@@ -1071,7 +1068,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B10" s="7">
@@ -1092,7 +1089,7 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="7">
@@ -1113,7 +1110,7 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B12" s="7">
@@ -1134,7 +1131,7 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="7">
@@ -1155,7 +1152,7 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B14" s="7">
@@ -1176,7 +1173,7 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="3" t="s">
         <v>10</v>
       </c>
       <c r="B15" s="7">
@@ -1197,7 +1194,7 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="7">
@@ -1218,7 +1215,7 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B17" s="7">
@@ -1239,7 +1236,7 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B18" s="7">
@@ -1260,7 +1257,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="3" t="s">
         <v>139</v>
       </c>
       <c r="B19" s="7">
@@ -1281,7 +1278,7 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="7">
@@ -1302,7 +1299,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="s">
+      <c r="A21" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="7">
@@ -1323,7 +1320,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B22" s="7">
@@ -1344,7 +1341,7 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="16" t="s">
+      <c r="A23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B23" s="7">
@@ -1365,7 +1362,7 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="3" t="s">
         <v>18</v>
       </c>
       <c r="B24" s="7">
@@ -1386,7 +1383,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
+      <c r="A25" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B25" s="7">
@@ -1407,7 +1404,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B26" s="7">
@@ -1428,7 +1425,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="16" t="s">
+      <c r="A27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="B27" s="7">
@@ -1449,7 +1446,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B28" s="7">
@@ -1470,7 +1467,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="16" t="s">
+      <c r="A29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B29" s="7">
@@ -1491,7 +1488,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="s">
+      <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
       <c r="B30" s="7">
@@ -1512,7 +1509,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="16" t="s">
+      <c r="A31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="B31" s="7">
@@ -1533,7 +1530,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="3" t="s">
         <v>26</v>
       </c>
       <c r="B32" s="7">
@@ -1554,7 +1551,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
+      <c r="A33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="B33" s="7">
@@ -1575,7 +1572,7 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
+      <c r="A34" s="3" t="s">
         <v>28</v>
       </c>
       <c r="B34" s="7">
@@ -1596,7 +1593,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" s="16" t="s">
+      <c r="A35" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B35" s="7">
@@ -1617,7 +1614,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A36" s="17" t="s">
+      <c r="A36" s="16" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="7">
@@ -1638,7 +1635,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B37" s="7">
@@ -1749,7 +1746,7 @@
       <c r="B42" s="7">
         <v>1</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="23" t="s">
         <v>73</v>
       </c>
       <c r="D42" s="6">
@@ -1902,10 +1899,10 @@
       <c r="B54" s="7">
         <v>1</v>
       </c>
-      <c r="D54" s="21">
+      <c r="D54" s="20">
         <v>32.450000000000003</v>
       </c>
-      <c r="E54" s="21">
+      <c r="E54" s="20">
         <f>D54/3</f>
         <v>10.816666666666668</v>
       </c>
@@ -1920,10 +1917,10 @@
       <c r="B55" s="7">
         <v>16</v>
       </c>
-      <c r="D55" s="19">
+      <c r="D55" s="18">
         <v>0.5</v>
       </c>
-      <c r="E55" s="21">
+      <c r="E55" s="20">
         <f>D55*B55</f>
         <v>8</v>
       </c>
@@ -1936,7 +1933,7 @@
       <c r="B57" s="7"/>
       <c r="C57" s="13"/>
       <c r="D57" s="6"/>
-      <c r="E57" s="19"/>
+      <c r="E57" s="18"/>
       <c r="F57" s="14"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
@@ -1958,7 +1955,7 @@
       <c r="F59" s="14"/>
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A60" s="18" t="s">
+      <c r="A60" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B60" s="7"/>
@@ -1974,13 +1971,13 @@
       <c r="B62" s="7">
         <v>3</v>
       </c>
-      <c r="C62" s="20" t="s">
+      <c r="C62" s="19" t="s">
         <v>92</v>
       </c>
       <c r="D62" s="6">
         <v>25.89</v>
       </c>
-      <c r="E62" s="19">
+      <c r="E62" s="18">
         <f>D62*B62</f>
         <v>77.67</v>
       </c>
@@ -1989,7 +1986,7 @@
       </c>
     </row>
     <row r="64" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A64" s="18" t="s">
+      <c r="A64" s="17" t="s">
         <v>82</v>
       </c>
       <c r="B64" s="7"/>
@@ -2009,7 +2006,7 @@
       <c r="D66" s="6">
         <v>38.950000000000003</v>
       </c>
-      <c r="E66" s="19">
+      <c r="E66" s="18">
         <f>D66*0</f>
         <v>0</v>
       </c>
@@ -2032,12 +2029,12 @@
       <c r="B68" s="7"/>
       <c r="C68" s="13"/>
       <c r="D68" s="6"/>
-      <c r="E68" s="19"/>
+      <c r="E68" s="18"/>
       <c r="F68" s="14"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
-      <c r="D69" s="22"/>
+      <c r="D69" s="21"/>
     </row>
     <row r="70" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
@@ -2046,10 +2043,10 @@
       <c r="B70" s="7">
         <v>1</v>
       </c>
-      <c r="D70" s="22">
+      <c r="D70" s="21">
         <v>12.4</v>
       </c>
-      <c r="E70" s="23">
+      <c r="E70" s="22">
         <f>D70*B70</f>
         <v>12.4</v>
       </c>
@@ -2064,10 +2061,10 @@
       <c r="B71" s="7">
         <v>1</v>
       </c>
-      <c r="D71" s="22">
+      <c r="D71" s="21">
         <v>5</v>
       </c>
-      <c r="E71" s="23">
+      <c r="E71" s="22">
         <f>D71*B71</f>
         <v>5</v>
       </c>
@@ -2076,7 +2073,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A72" s="18"/>
+      <c r="A72" s="17"/>
       <c r="B72" s="7"/>
       <c r="C72" s="2"/>
       <c r="D72" s="6"/>
@@ -2087,7 +2084,7 @@
       <c r="B74" s="7"/>
       <c r="C74" s="13"/>
       <c r="D74" s="6"/>
-      <c r="E74" s="19"/>
+      <c r="E74" s="18"/>
       <c r="F74" s="14"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
@@ -2095,23 +2092,23 @@
       <c r="B79" s="7"/>
       <c r="C79" s="13"/>
       <c r="D79" s="6"/>
-      <c r="E79" s="19"/>
+      <c r="E79" s="18"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="2"/>
-      <c r="D80" s="22"/>
+      <c r="D80" s="21"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="B81" s="7"/>
-      <c r="D81" s="22"/>
-      <c r="E81" s="23"/>
+      <c r="D81" s="21"/>
+      <c r="E81" s="22"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="B82" s="7"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="23"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
